--- a/02-Test-Cases/FB_Login_TestCases.xlsx
+++ b/02-Test-Cases/FB_Login_TestCases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ql3ql\Desktop\Review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ql3ql\Desktop\resume\Review\Test-Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D220CF0-EB81-4823-96EA-B23592206773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65911825-053A-47EA-B3DE-D4608EE920B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{D69C6F5C-DFF2-4CC3-9B1B-941035C66C29}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="138">
   <si>
     <t>點擊"登入"按鈕</t>
   </si>
@@ -462,6 +462,9 @@
   </si>
   <si>
     <t>電話號碼或電子郵件欄位留空進行登入</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -579,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -593,18 +596,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -627,7 +623,6 @@
     <xf numFmtId="176" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -637,12 +632,6 @@
     <xf numFmtId="49" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -651,6 +640,19 @@
     </xf>
     <xf numFmtId="1" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1103,7 +1105,7 @@
     <tabColor rgb="FF6AA84F"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="6.33203125" customWidth="1"/>
@@ -1112,595 +1114,584 @@
     <col min="4" max="4" width="14.21875" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="14.21875" customWidth="1"/>
-    <col min="7" max="7" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:6" ht="15.6">
+      <c r="A1" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="15"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="14" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.6">
-      <c r="A3" s="12">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.6">
+      <c r="A3" s="9">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="10"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="7" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:6">
+      <c r="A7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="15.6">
-      <c r="A8" s="12">
+    <row r="8" spans="1:6" ht="15.6">
+      <c r="A8" s="9">
         <v>2</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="11" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="10"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="7" t="s">
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="3"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="3"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="3"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="31.2">
-      <c r="A13" s="12">
+    <row r="13" spans="1:6" ht="31.2">
+      <c r="A13" s="9">
         <v>3</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="10"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="7" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="26.4">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:6" ht="26.4">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="3"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="3"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:6">
+      <c r="A17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="3"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="31.2">
-      <c r="A18" s="12">
+    <row r="18" spans="1:6" ht="31.2">
+      <c r="A18" s="9">
         <v>4</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="10"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="7" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="26.4">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:6" ht="26.4">
+      <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="3"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:6">
+      <c r="A21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="3"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:6">
+      <c r="A22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="3"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:7" ht="15.6">
-      <c r="A23" s="12">
+    <row r="23" spans="1:6" ht="15.6">
+      <c r="A23" s="9">
         <v>5</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="11" t="s">
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="10"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="7" t="s">
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="26.4">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:6" ht="26.4">
+      <c r="A25" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="3"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:6">
+      <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="3"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:6">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="3"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
-      <c r="A28" s="12">
+    <row r="28" spans="1:6" ht="15.6">
+      <c r="A28" s="9">
         <v>6</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="10"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="7" t="s">
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="22" t="s">
         <v>6</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:7" ht="26.4">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:6" ht="26.4">
+      <c r="A30" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="3"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:6">
+      <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="3"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:6">
+      <c r="A32" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="3"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="1:7" ht="31.2">
-      <c r="A33" s="12">
+    <row r="33" spans="1:6" ht="31.2">
+      <c r="A33" s="9">
         <v>7</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="10"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="7" t="s">
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="22" t="s">
         <v>6</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:7" ht="26.4">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:6" ht="26.4">
+      <c r="A35" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="3"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:6">
+      <c r="A36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="3"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:6">
+      <c r="A37" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="3"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:7" ht="31.2">
-      <c r="A38" s="12">
+    <row r="38" spans="1:6" ht="31.2">
+      <c r="A38" s="9">
         <v>8</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="10"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="7" t="s">
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="22" t="s">
         <v>6</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="1:7" ht="26.4">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:6" ht="26.4">
+      <c r="A40" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="3"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="7" t="s">
+    <row r="41" spans="1:6">
+      <c r="A41" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="3"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:6">
+      <c r="A42" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="3"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:6">
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:6">
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:6">
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:6">
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:6">
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:6">
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="3:6">
@@ -1893,7 +1884,7 @@
     <tabColor rgb="FF6AA84F"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.33203125" customWidth="1"/>
@@ -1902,1076 +1893,1055 @@
     <col min="4" max="4" width="14.21875" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="14.21875" customWidth="1"/>
-    <col min="7" max="7" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:6" ht="15.6">
+      <c r="A1" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="15"/>
-    </row>
-    <row r="2" spans="1:7" ht="13.2">
-      <c r="A2" s="14" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="13.2">
+      <c r="A2" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.6">
-      <c r="A3" s="12">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.6">
+      <c r="A3" s="9">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="10"/>
-    </row>
-    <row r="4" spans="1:7" ht="13.2">
-      <c r="A4" s="7" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="13.2">
+      <c r="A4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="13.2">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:6" ht="13.2">
+      <c r="A5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="13.2">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:6" ht="13.2">
+      <c r="A6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="13.2">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:6" ht="13.2">
+      <c r="A7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="15.6">
-      <c r="A8" s="12">
+    <row r="8" spans="1:6" ht="15.6">
+      <c r="A8" s="9">
         <v>2</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="11" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="10"/>
-    </row>
-    <row r="9" spans="1:7" ht="13.2">
-      <c r="A9" s="7" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="13.2">
+      <c r="A9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="13.2">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:6" ht="13.2">
+      <c r="A10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="3"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="13.2">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:6" ht="13.2">
+      <c r="A11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="3"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="13.2">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:6" ht="13.2">
+      <c r="A12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="3"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="15.6">
-      <c r="A13" s="12">
+    <row r="13" spans="1:6" ht="15.6">
+      <c r="A13" s="9">
         <v>3</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="13.2">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:6" ht="13.2">
+      <c r="A14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="13.2">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:6" ht="13.2">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="3"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="13.2">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:6" ht="13.2">
+      <c r="A16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="3"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:7" ht="13.2">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:6" ht="13.2">
+      <c r="A17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="3"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="15.6">
-      <c r="A18" s="12">
+    <row r="18" spans="1:6" ht="15.6">
+      <c r="A18" s="9">
         <v>4</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="11" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="10"/>
-    </row>
-    <row r="19" spans="1:7" ht="13.2">
-      <c r="A19" s="7" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="13.2">
+      <c r="A19" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="13.2">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:6" ht="13.2">
+      <c r="A20" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="3"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:7" ht="13.2">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:6" ht="13.2">
+      <c r="A21" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="3"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="13.2">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:6" ht="13.2">
+      <c r="A22" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="3"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:7" ht="15.6">
-      <c r="A23" s="12">
+    <row r="23" spans="1:6" ht="15.6">
+      <c r="A23" s="9">
         <v>5</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="11" t="s">
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="10"/>
-    </row>
-    <row r="24" spans="1:7" ht="13.2">
-      <c r="A24" s="7" t="s">
+    </row>
+    <row r="24" spans="1:6" ht="13.2">
+      <c r="A24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="26.4">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:6" ht="26.4">
+      <c r="A25" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="3"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:7" ht="13.2">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:6" ht="13.2">
+      <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="3"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:7" ht="13.2">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:6" ht="13.2">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="3"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
-      <c r="A28" s="12">
+    <row r="28" spans="1:6" ht="15.6">
+      <c r="A28" s="9">
         <v>6</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="11" t="s">
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G28" s="10"/>
-    </row>
-    <row r="29" spans="1:7" ht="13.2">
-      <c r="A29" s="7" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="13.2">
+      <c r="A29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:7" ht="13.2">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:6" ht="13.2">
+      <c r="A30" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="3"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:7" ht="13.2">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:6" ht="13.2">
+      <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="3"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:7" ht="13.2">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:6" ht="13.2">
+      <c r="A32" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="3"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="1:7" ht="15.6">
-      <c r="A33" s="25">
+    <row r="33" spans="1:6" ht="15.6">
+      <c r="A33" s="19">
         <v>7</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="24" t="s">
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="23"/>
-    </row>
-    <row r="34" spans="1:7" ht="13.2">
-      <c r="A34" s="20" t="s">
+    </row>
+    <row r="34" spans="1:6" ht="13.2">
+      <c r="A34" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="19"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="17"/>
-    </row>
-    <row r="35" spans="1:7" ht="26.4">
-      <c r="A35" s="20" t="s">
+      <c r="E34" s="15"/>
+      <c r="F34" s="14"/>
+    </row>
+    <row r="35" spans="1:6" ht="26.4">
+      <c r="A35" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="17"/>
-    </row>
-    <row r="36" spans="1:7" ht="13.2">
-      <c r="A36" s="20" t="s">
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="14"/>
+    </row>
+    <row r="36" spans="1:6" ht="13.2">
+      <c r="A36" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="17"/>
-    </row>
-    <row r="37" spans="1:7" ht="13.2">
-      <c r="A37" s="20" t="s">
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="14"/>
+    </row>
+    <row r="37" spans="1:6" ht="13.2">
+      <c r="A37" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="17"/>
-    </row>
-    <row r="38" spans="1:7" ht="15.6">
-      <c r="A38" s="12">
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="14"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.6">
+      <c r="A38" s="9">
         <v>8</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="11" t="s">
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G38" s="10"/>
-    </row>
-    <row r="39" spans="1:7" ht="13.2">
-      <c r="A39" s="7" t="s">
+    </row>
+    <row r="39" spans="1:6" ht="13.2">
+      <c r="A39" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="22" t="s">
         <v>31</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="1:7" ht="13.2">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:6" ht="13.2">
+      <c r="A40" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="3"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="1:7" ht="13.2">
-      <c r="A41" s="7" t="s">
+    <row r="41" spans="1:6" ht="13.2">
+      <c r="A41" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="3"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="1:7" ht="13.2">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:6" ht="13.2">
+      <c r="A42" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="3"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="1:7" ht="15.6">
-      <c r="A43" s="12">
+    <row r="43" spans="1:6" ht="15.6">
+      <c r="A43" s="9">
         <v>9</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="11" t="s">
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G43" s="10"/>
-    </row>
-    <row r="44" spans="1:7" ht="13.2">
-      <c r="A44" s="7" t="s">
+    </row>
+    <row r="44" spans="1:6" ht="13.2">
+      <c r="A44" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>6</v>
+      <c r="D44" s="22" t="s">
+        <v>31</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="1:7" ht="13.2">
-      <c r="A45" s="7" t="s">
+    <row r="45" spans="1:6" ht="13.2">
+      <c r="A45" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="3"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:7" ht="13.2">
-      <c r="A46" s="7" t="s">
+    <row r="46" spans="1:6" ht="13.2">
+      <c r="A46" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="3"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="1:7" ht="13.2">
-      <c r="A47" s="7" t="s">
+    <row r="47" spans="1:6" ht="13.2">
+      <c r="A47" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="3"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="1:7" ht="15.6">
-      <c r="A48" s="12">
+    <row r="48" spans="1:6" ht="15.6">
+      <c r="A48" s="9">
         <v>10</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="10"/>
-    </row>
-    <row r="49" spans="1:7" ht="13.2">
-      <c r="A49" s="7" t="s">
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="13.2">
+      <c r="A49" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>6</v>
+      <c r="D49" s="22" t="s">
+        <v>31</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="1:7" ht="26.4">
-      <c r="A50" s="7" t="s">
+    <row r="50" spans="1:6" ht="26.4">
+      <c r="A50" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="3"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" spans="1:7" ht="13.2">
-      <c r="A51" s="7" t="s">
+    <row r="51" spans="1:6" ht="13.2">
+      <c r="A51" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="3"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="1:7" ht="13.2">
-      <c r="A52" s="7" t="s">
+    <row r="52" spans="1:6" ht="13.2">
+      <c r="A52" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="3"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="1:7" ht="13.2">
-      <c r="A53" s="7" t="s">
+    <row r="53" spans="1:6" ht="13.2">
+      <c r="A53" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="3"/>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" spans="1:7" ht="31.2">
-      <c r="A54" s="12">
+    <row r="54" spans="1:6" ht="31.2">
+      <c r="A54" s="9">
         <v>11</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="11" t="s">
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="G54" s="10"/>
-    </row>
-    <row r="55" spans="1:7" ht="13.2">
-      <c r="A55" s="7" t="s">
+    </row>
+    <row r="55" spans="1:6" ht="13.2">
+      <c r="A55" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D55" s="8" t="s">
-        <v>6</v>
+      <c r="D55" s="22" t="s">
+        <v>31</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" spans="1:7" ht="26.4">
-      <c r="A56" s="7" t="s">
+    <row r="56" spans="1:6" ht="26.4">
+      <c r="A56" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="3"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="1:7" ht="13.2">
-      <c r="A57" s="7" t="s">
+    <row r="57" spans="1:6" ht="13.2">
+      <c r="A57" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="3"/>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="1:7" ht="13.2">
-      <c r="A58" s="7" t="s">
+    <row r="58" spans="1:6" ht="13.2">
+      <c r="A58" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
       <c r="E58" s="3"/>
       <c r="F58" s="2"/>
     </row>
-    <row r="59" spans="1:7" ht="13.2">
-      <c r="A59" s="7" t="s">
+    <row r="59" spans="1:6" ht="13.2">
+      <c r="A59" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
       <c r="E59" s="3"/>
       <c r="F59" s="2"/>
     </row>
-    <row r="60" spans="1:7" ht="26.4">
-      <c r="A60" s="7" t="s">
+    <row r="60" spans="1:6" ht="26.4">
+      <c r="A60" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
       <c r="E60" s="3"/>
       <c r="F60" s="2"/>
     </row>
-    <row r="61" spans="1:7" ht="15.6">
-      <c r="A61" s="12">
+    <row r="61" spans="1:6" ht="15.6">
+      <c r="A61" s="9">
         <v>12</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="10"/>
-    </row>
-    <row r="62" spans="1:7" ht="13.2">
-      <c r="A62" s="7" t="s">
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="13.2">
+      <c r="A62" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D62" s="8" t="s">
-        <v>6</v>
+      <c r="D62" s="22" t="s">
+        <v>31</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" spans="1:7" ht="26.4">
-      <c r="A63" s="7" t="s">
+    <row r="63" spans="1:6" ht="26.4">
+      <c r="A63" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
       <c r="E63" s="3"/>
       <c r="F63" s="2"/>
     </row>
-    <row r="64" spans="1:7" ht="13.2">
-      <c r="A64" s="7" t="s">
+    <row r="64" spans="1:6" ht="13.2">
+      <c r="A64" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
       <c r="E64" s="3"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="1:7" ht="13.2">
-      <c r="A65" s="7" t="s">
+    <row r="65" spans="1:6" ht="13.2">
+      <c r="A65" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
       <c r="E65" s="3"/>
       <c r="F65" s="2"/>
     </row>
-    <row r="66" spans="1:7" ht="15.6">
-      <c r="A66" s="12">
+    <row r="66" spans="1:6" ht="15.6">
+      <c r="A66" s="9">
         <v>13</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" s="10"/>
-    </row>
-    <row r="67" spans="1:7" ht="13.2">
-      <c r="A67" s="7" t="s">
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="13.2">
+      <c r="A67" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D67" s="8" t="s">
-        <v>6</v>
+      <c r="D67" s="22" t="s">
+        <v>31</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="2"/>
     </row>
-    <row r="68" spans="1:7" ht="26.4">
-      <c r="A68" s="7" t="s">
+    <row r="68" spans="1:6" ht="26.4">
+      <c r="A68" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
       <c r="E68" s="3"/>
       <c r="F68" s="2"/>
     </row>
-    <row r="69" spans="1:7" ht="13.2">
-      <c r="A69" s="7" t="s">
+    <row r="69" spans="1:6" ht="13.2">
+      <c r="A69" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
       <c r="E69" s="3"/>
       <c r="F69" s="2"/>
     </row>
-    <row r="70" spans="1:7" ht="13.2">
-      <c r="A70" s="7" t="s">
+    <row r="70" spans="1:6" ht="13.2">
+      <c r="A70" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
       <c r="E70" s="3"/>
       <c r="F70" s="2"/>
     </row>
-    <row r="71" spans="1:7" ht="15.6">
-      <c r="A71" s="12">
+    <row r="71" spans="1:6" ht="15.6">
+      <c r="A71" s="9">
         <v>14</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="G71" s="10"/>
-    </row>
-    <row r="72" spans="1:7" ht="13.2">
-      <c r="A72" s="7" t="s">
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="13.2">
+      <c r="A72" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D72" s="8" t="s">
-        <v>6</v>
+      <c r="D72" s="22" t="s">
+        <v>31</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="2"/>
     </row>
-    <row r="73" spans="1:7" ht="13.2">
-      <c r="A73" s="7" t="s">
+    <row r="73" spans="1:6" ht="13.2">
+      <c r="A73" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
       <c r="E73" s="3"/>
       <c r="F73" s="2"/>
     </row>
-    <row r="74" spans="1:7" ht="13.2">
-      <c r="A74" s="7" t="s">
+    <row r="74" spans="1:6" ht="13.2">
+      <c r="A74" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
       <c r="E74" s="3"/>
       <c r="F74" s="2"/>
     </row>
-    <row r="75" spans="1:7" ht="13.2">
-      <c r="A75" s="7" t="s">
+    <row r="75" spans="1:6" ht="13.2">
+      <c r="A75" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
       <c r="E75" s="3"/>
       <c r="F75" s="2"/>
     </row>
-    <row r="76" spans="1:7" ht="15.6">
-      <c r="A76" s="12">
+    <row r="76" spans="1:6" ht="15.6">
+      <c r="A76" s="9">
         <v>15</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B76" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G76" s="10"/>
-    </row>
-    <row r="77" spans="1:7" ht="13.2">
-      <c r="A77" s="7" t="s">
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="13.2">
+      <c r="A77" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="22" t="s">
         <v>6</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" spans="1:7" ht="26.4">
-      <c r="A78" s="7" t="s">
+    <row r="78" spans="1:6" ht="26.4">
+      <c r="A78" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
       <c r="E78" s="3"/>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" spans="1:7" ht="13.2">
-      <c r="A79" s="7" t="s">
+    <row r="79" spans="1:6" ht="13.2">
+      <c r="A79" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
       <c r="E79" s="3"/>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" spans="1:7" ht="13.2">
+    <row r="80" spans="1:6" ht="13.2">
       <c r="F80" s="2"/>
     </row>
     <row r="81" spans="3:6" ht="13.2">
@@ -3078,8 +3048,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="D49:D53"/>
-    <mergeCell ref="D55:D60"/>
     <mergeCell ref="C72:C75"/>
     <mergeCell ref="C77:C79"/>
     <mergeCell ref="D62:D65"/>
@@ -3096,6 +3064,8 @@
     <mergeCell ref="C44:C47"/>
     <mergeCell ref="D44:D47"/>
     <mergeCell ref="C49:C53"/>
+    <mergeCell ref="D49:D53"/>
+    <mergeCell ref="D55:D60"/>
     <mergeCell ref="D19:D22"/>
     <mergeCell ref="C19:C22"/>
     <mergeCell ref="C24:C27"/>
@@ -3148,5 +3118,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>